--- a/yosou_db_11stores.xlsx
+++ b/yosou_db_11stores.xlsx
@@ -236,7 +236,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -439,6 +439,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4893,7 +4894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="26" customWidth="1" style="29" min="1" max="1"/>
@@ -5003,6 +5004,18 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="70" t="inlineStr">
+        <is>
+          <t>サイトセブン(契約済)</t>
+        </is>
+      </c>
+      <c r="B11" s="69" t="inlineStr">
+        <is>
+          <t>加盟4店: SAP草加/ピーアーク草加/楽園南越谷/パラッツォ馬橋駅前。答え合わせの精査用(人の閲覧ペースで前夜予想店×機種のみ確認)。非加盟7店は従来ソース+各公式チャネル。※パラッツォ三郷中央は非加盟だが系列の三郷店(新和)が加盟=系列のクセ観察に利用可</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
